--- a/data/file_generation/input/data_211/2026届高三10月月考学生拟表彰名单.xlsx
+++ b/data/file_generation/input/data_211/2026届高三10月月考学生拟表彰名单.xlsx
@@ -904,18 +904,26 @@
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
+  <documentManagement>
+    <SharedWithUsers xmlns="eca6eae4-1627-4e8d-9a6b-5b4dd91506e7">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+  </documentManagement>
 </p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{381B654E-F50E-4074-A4AA-0DA23853FF76}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5297FBE9-5550-4FF7-94B4-E99684E37F08}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8A17110C-4B6E-43BB-95BD-4A81B36CAAD1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1545E9D1-738D-42CF-9FFB-A62535E9AE2A}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{23A7106E-A738-47DD-B107-838ADD6FF967}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{45E9FE99-4389-46D3-94DA-968524AD2B59}"/>
 </file>